--- a/00 - Docs/02 - GPS_Docs/ACwing_GPS_A_CPL.xlsx
+++ b/00 - Docs/02 - GPS_Docs/ACwing_GPS_A_CPL.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15.0000mm</t>
+          <t>18.6000mm</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
